--- a/output/job_application_status.xlsx
+++ b/output/job_application_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,6 +551,519 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ZinCaT Technology</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Product Delivery Assistant Manager – Software Development</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/product-delivery-assistant-manager-%E2%80%93-software-development-at-zincat-technology-4322622250</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Wavenet</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Delivery Lead - Cloud</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/delivery-lead-cloud-at-wavenet-3513740457</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Skilled Search Sri Lanka</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Service Delivery Manager</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/service-delivery-manager-at-skilled-search-sri-lanka-4397686265</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Easor Finland</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Engineering Manager, Developer Experience</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/engineering-manager-developer-experience-at-easor-finland-1234567890</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HiQ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DevOps Specialist</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/job-listing/devops-specialist-hiq-JV_IC2287361_KO0,16_KE17,20.htm</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GovTech Sri Lanka</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/senior-software-architect-at-govtech-sri-lanka-4329608881</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Homey</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/senior-software-architect-at-homey-4377841992</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IFS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Software Architect / Senior Software Architect : DevOps - Cloud Engineering (R&amp;D)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/software-architect-senior-software-architect-devops-cloud-engineering-r-d-at-ifs-4203757659</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mind Plus</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/senior-software-architect-at-mind-plus-3683613823</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Onsys Technologies</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Senior Software Architect</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/senior-software-architect-at-onsys-technologies-4273202319</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Reaktor</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hands-on Software Architect</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Job/finland-java-architect-jobs-SRCH_IL.0,7_IN79_KO8,22.htm</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Virnex Oy</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Software Engineer/Data Engineer</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://meetfrank.com/jobs/virnex-oy/software-engineerdata-engineer-2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rakettitiede oy</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://meetfrank.com/latest-c-sharp-development-jobs-in-finland</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ArcTerns</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Java Architect</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/java-architect-at-arcterns-2943848217</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Acentura Inc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tech lead / Associate Architect – DevOps</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/tech-lead-associate-architect-–-devops-at-acentura-inc-3775973290</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kognitiv Corporation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (AWS)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://lk.linkedin.com/jobs/view/devops-engineer-aws-at-kognitiv-corporation-3408839930</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Software Architect</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Job/finland-software-architect-jobs-SRCH_IL.0,7_IN79_KO8,26.htm</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Confidential</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Software Architect in a software product development unit</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Job/finland-software-developer-jobs-SRCH_IL.0,7_IN79_KO8,26.htm</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Confidential</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Cloud Architect Azure</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Job/helsinki-cloud-architect-azure-jobs-SRCH_IL.0,8_IC2440450_KO9,30.htm</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/job_application_status.xlsx
+++ b/output/job_application_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,6 +1064,60 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>.NET Architect Jobs in Finland</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Job/finland-net-architect-jobs-SRCH_IL.0,7_IN79_KO8,21.htm</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DevOps Jobs in Finland</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Job/finland-devops-jobs-SRCH_IL.0,7_IN79_KO8,14.htm</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
